--- a/data/raw/sales/Week 27/Nexlev/Seller Sales (SP-API).xlsx
+++ b/data/raw/sales/Week 27/Nexlev/Seller Sales (SP-API).xlsx
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>4487.29</v>
+        <v>3589.83</v>
       </c>
       <c r="H28" t="n">
         <v>340</v>
